--- a/组合介绍/report_assets/factors/workbooks/4-Microsoft_Excel_Worksheet4.xlsx
+++ b/组合介绍/report_assets/factors/workbooks/4-Microsoft_Excel_Worksheet4.xlsx
@@ -65,7 +65,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -73,6 +72,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -125,10 +125,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+      <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,35 +451,35 @@
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="19"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="str">
+      <c r="A1" s="2" t="str">
         <v>货币因子状态</v>
       </c>
-      <c r="B1" s="1" t="str">
+      <c r="B1" s="2" t="str">
         <v>利率含义</v>
       </c>
-      <c r="C1" s="1" t="str">
+      <c r="C1" s="2" t="str">
         <v>货币环境</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="str">
+      <c r="A2" s="1" t="str">
         <v>货币因子 &gt; 0</v>
       </c>
-      <c r="B2" s="2" t="str">
+      <c r="B2" s="1" t="str">
         <v>短端利率高于趋势</v>
       </c>
-      <c r="C2" s="2" t="str">
+      <c r="C2" s="1" t="str">
         <v>偏紧</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="str">
+      <c r="A3" s="1" t="str">
         <v>货币因子 ≤ 0</v>
       </c>
-      <c r="B3" s="2" t="str">
+      <c r="B3" s="1" t="str">
         <v>短端利率低于趋势</v>
       </c>
-      <c r="C3" s="2" t="str">
+      <c r="C3" s="1" t="str">
         <v>偏宽松</v>
       </c>
     </row>
